--- a/Side Bar Files/GWD Data/PVC on Wall.xlsx
+++ b/Side Bar Files/GWD Data/PVC on Wall.xlsx
@@ -879,7 +879,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D8C868-46AD-4C0E-B9B4-DFE13A3ABAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5726249D-4C8F-40F2-93A9-546E561EBAA6}">
   <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC on Wall.xlsx
+++ b/Side Bar Files/GWD Data/PVC on Wall.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -524,10 +524,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -879,7 +879,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5726249D-4C8F-40F2-93A9-546E561EBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1488D9AE-0F51-436A-9F54-FB1AF2FBBAA6}">
   <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
